--- a/Luban/Config/Datas/Levels/L28/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L28/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L28 W1/25; N=58; EHP=387.904000; normal:17x29,normal:18x29</t>
+          <t>L28 W1/25; N=58; EHP=1073.891569; normal:17x29,normal:18x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L28 W2/25; N=64; EHP=448.192307; normal:17x32,normal:18x32</t>
+          <t>L28 W2/25; N=64; EHP=1240.796537; normal:17x32,normal:18x32 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10021174,10021176,10049097,10021174,10021176,10049097,10021174,10021176,10049098,10021174,10021176,10049099,10021174,10021176,10049099,10021174,10021176,10049100,10021174,10021176,10049100,10021174,10021176,10049101,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021174,10021174,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175</t>
+          <t>10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021176,10021174,10021174,10021174,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021175,10021174,10021174,10021174,10021174,10021174,10021174,10021174,10021174</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L28 W3/25; N=70; EHP=542.316544; air:2x2,air:11x1,air:12x2,air:13x2,air:14x1,normal:17x22,normal:18x21,swarm:84x19</t>
+          <t>L28 W3/25; N=70; EHP=1613.436353; normal:17x30,normal:18x21,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10021177,10021179,10049102,10021177,10021179,10049102,10021177,10021179,10049103,10021177,10021179,10049103,10021177,10021179,10049104,10021177,10021179,10049105,10021177,10021179,10049105,10021177,10021179,10049106,10021177,10021179,10049106,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021177,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178</t>
+          <t>10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021179,10021177,10021177,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021178,10021177,10021177,10021177,10021177,10021177,10021177,10021177,10021177,10021177</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L28 W4/25; N=76; EHP=680.000000; air:2x2,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x23,normal:18x23,swarm:84x21</t>
+          <t>L28 W4/25; N=76; EHP=2028.832517; normal:17x32,normal:18x23,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10021180,10021183,10049107,10021182,10021180,10021183,10049107,10021182,10021180,10021183,10049108,10021182,10021180,10021183,10049108,10021182,10021180,10021183,10049109,10021184,10021180,10021183,10049109,10021184,10021180,10021183,10049110,10021184,10021180,10021183,10049110,10021184,10021180,10021183,10049111,10021185,10021180,10021183,10049111,10021185,10021180,10021183,10021185,10021180,10021183,10021185,10021180,10021183,10021180,10021183,10021180,10021183,10021180,10021183,10021180,10021183,10021180,10021183,10021180,10021183,10021181,10021183,10021181,10021183,10021181,10021183,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181</t>
+          <t>10021180,10049107,10049107,10021182,10021180,10049107,10049107,10021182,10021180,10049108,10049108,10021182,10021180,10049108,10049108,10021182,10021180,10049109,10049109,10021184,10021180,10049109,10049109,10021184,10021180,10049110,10049110,10021184,10021180,10049110,10049110,10021184,10021180,10049111,10049111,10021185,10021180,10049111,10049111,10021185,10021180,10021183,10021185,10021180,10021183,10021185,10021180,10021183,10021180,10021183,10021180,10021183,10021180,10021183,10021180,10021183,10021180,10021183,10021180,10021183,10021181,10021183,10021181,10021183,10021181,10021183,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181,10021181</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L28 W5/25; N=82; EHP=1266.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x19,normal:18x19,medium:83x4,swarm:84x22,medium:108x4,medium:123x4</t>
+          <t>L28 W5/25; N=82; EHP=3550.253247; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x4,medium:123x4,normal:17x19,normal:18x19,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10021189,10021195,10021191,10049112,10021194,10021189,10021195,10021191,10049112,10021194,10021189,10021195,10021192,10021186,10021194,10021189,10021195,10021192,10021186,10021194,10021189,10021195,10021192,10021186,10021197,10021189,10021195,10021193,10049113,10021197,10021189,10021195,10021193,10049113,10021197,10021189,10021195,10021193,10021187,10021197,10021189,10021195,10021196,10021187,10021198,10021189,10021195,10021196,10021188,10021198,10021189,10021195,10021188,10021198,10021189,10021195,10021198,10021189,10021195,10021198,10021189,10021195,10021189,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021190,10021190,10021190,10021190,10021190</t>
+          <t>10021189,10049112,10021191,10049112,10021194,10021189,10049112,10021191,10049112,10021194,10021189,10021186,10021192,10021186,10021194,10021189,10021186,10021192,10021186,10021194,10021189,10021186,10021192,10021186,10021197,10021189,10049113,10021193,10049113,10021197,10021189,10049113,10021193,10049113,10021197,10021189,10021187,10021193,10021187,10021197,10021189,10021187,10021196,10021187,10021198,10021189,10021188,10021196,10021188,10021198,10021189,10021188,10021188,10021198,10021189,10021195,10021198,10021189,10021195,10021198,10021189,10021195,10021189,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021195,10021190,10021190,10021190,10021190,10021190,10021190</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L28 W6/25; N=88; EHP=1292.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x24,fast:98x2,medium:108x4,medium:123x5</t>
+          <t>L28 W6/25; N=88; EHP=3625.317697; air:2x4,air:11x6,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x5,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10021202,10021208,10021204,10049114,10021207,10021202,10021208,10021204,10049114,10021207,10021202,10021208,10021204,10021199,10021207,10021202,10021208,10021205,10021199,10021207,10021202,10021208,10021205,10049115,10021207,10021202,10021208,10021206,10049115,10021210,10021202,10021208,10021206,10021200,10021210,10021202,10021208,10021206,10021200,10021210,10021202,10021208,10021209,10021201,10021210,10021202,10021208,10021209,10021201,10021210,10021202,10021208,10021209,10021201,10021211,10021202,10021208,10021211,10021202,10021208,10021211,10021202,10021208,10021211,10021202,10021208,10021202,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021203,10021203,10021203,10021203,10021203</t>
+          <t>10021202,10049114,10021204,10049114,10021207,10021202,10049114,10021204,10049114,10021207,10021202,10021199,10021204,10021199,10021207,10021202,10021199,10021205,10021199,10021207,10021202,10049115,10021205,10049115,10021207,10021202,10049115,10021206,10049115,10021210,10021202,10021200,10021206,10021200,10021210,10021202,10021200,10021206,10021200,10021210,10021202,10021201,10021209,10021201,10021210,10021202,10021201,10021209,10021201,10021210,10021202,10021201,10021209,10021201,10021211,10021202,10021208,10021211,10021202,10021208,10021211,10021202,10021208,10021211,10021202,10021208,10021202,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021208,10021203,10021203,10021203,10021203,10021203,10021203</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L28 W7/25; N=94; EHP=1449.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x3,normal:17x16,normal:18x16,fast:30x3,fast:58x2,fast:64x3,medium:83x5,swarm:84x26,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L28 W7/25; N=94; EHP=4062.199199; air:2x4,air:11x4,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x2,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x4,normal:17x16,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10021215,10021221,10021217,10049116,10021220,10021215,10021221,10021217,10049116,10021220,10021215,10021221,10021217,10049116,10021220,10021215,10021221,10021218,10021212,10021220,10021215,10021221,10021218,10021212,10021220,10021215,10021221,10021218,10049117,10021223,10021215,10021221,10021219,10049117,10021223,10021215,10021221,10021219,10049117,10021223,10021215,10021221,10021219,10021213,10021223,10021215,10021221,10021222,10021213,10021223,10021215,10021221,10021222,10021214,10021224,10021215,10021221,10021222,10021214,10021224,10021215,10021221,10021224,10021215,10021221,10021224,10021215,10021221,10021224,10021215,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021216,10021216,10021216,10021216</t>
+          <t>10021215,10049116,10021217,10049116,10021220,10021215,10049116,10021217,10049116,10021220,10021215,10049116,10021217,10049116,10021220,10021215,10021212,10021218,10021212,10021220,10021215,10021212,10021218,10021212,10021220,10021215,10049117,10021218,10049117,10021223,10021215,10049117,10021219,10049117,10021223,10021215,10049117,10021219,10049117,10021223,10021215,10021213,10021219,10021213,10021223,10021215,10021213,10021222,10021213,10021223,10021215,10021214,10021222,10021214,10021224,10021215,10021214,10021222,10021214,10021224,10021215,10021221,10021224,10021215,10021221,10021224,10021215,10021221,10021224,10021215,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021221,10021216,10021216,10021216,10021216,10021216</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L28 W8/25; N=100; EHP=1861.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x16,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L28 W8/25; N=100; EHP=5219.062021; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x16,normal:18x17,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10021228,10021234,10021230,10049118,10021233,10021228,10021234,10021230,10049118,10021233,10021228,10021234,10021230,10049118,10021233,10021228,10021234,10021231,10021225,10021233,10021228,10021234,10021231,10021225,10021233,10021228,10021234,10021231,10021225,10021236,10021228,10021234,10021232,10049119,10021236,10021228,10021234,10021232,10049119,10021236,10021228,10021234,10021232,10021226,10021236,10021228,10021234,10021235,10021226,10021236,10021228,10021234,10021235,10021226,10021237,10021228,10021234,10021235,10021227,10021237,10021228,10021234,10021227,10021237,10021228,10021234,10021237,10021228,10021234,10021237,10021228,10021234,10021228,10021234,10021228,10021234,10021228,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021229,10021229,10021229,10021229,10021229,10021229,10021229</t>
+          <t>10021228,10049118,10021230,10049118,10021233,10021228,10049118,10021230,10049118,10021233,10021228,10049118,10021230,10049118,10021233,10021228,10021225,10021231,10021225,10021233,10021228,10021225,10021231,10021225,10021233,10021228,10021225,10021231,10021225,10021236,10021228,10049119,10021232,10049119,10021236,10021228,10049119,10021232,10049119,10021236,10021228,10021226,10021232,10021226,10021236,10021228,10021226,10021235,10021226,10021236,10021228,10021226,10021235,10021226,10021237,10021228,10021227,10021235,10021227,10021237,10021228,10021227,10021227,10021237,10021228,10021234,10021237,10021228,10021234,10021237,10021228,10021234,10021228,10021234,10021228,10021234,10021228,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021234,10021229,10021229,10021229,10021229,10021229,10021229,10021229,10021229</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L28 W9/25; N=106; EHP=2373.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x19,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x29,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L28 W9/25; N=106; EHP=6657.207732; air:2x6,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x19,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10021241,10021247,10021243,10049120,10021246,10021241,10021247,10021243,10049120,10021246,10021241,10021247,10021243,10021238,10021246,10021241,10021247,10021244,10021238,10021246,10021241,10021247,10021244,10021238,10021246,10021241,10021247,10021244,10049121,10021249,10021241,10021247,10021244,10049121,10021249,10021241,10021247,10021245,10021239,10021249,10021241,10021247,10021245,10021239,10021249,10021241,10021247,10021245,10021239,10021249,10021241,10021247,10021248,10021240,10021249,10021241,10021247,10021248,10021240,10021250,10021241,10021247,10021248,10021240,10021250,10021241,10021247,10021250,10021241,10021247,10021250,10021241,10021247,10021250,10021241,10021247,10021241,10021247,10021241,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021242,10021242,10021242,10021242,10021242,10021242,10021242</t>
+          <t>10021241,10049120,10021243,10049120,10021246,10021241,10049120,10021243,10049120,10021246,10021241,10021238,10021243,10021238,10021246,10021241,10021238,10021244,10021238,10021246,10021241,10021238,10021244,10021238,10021246,10021241,10049121,10021244,10049121,10021249,10021241,10049121,10021244,10049121,10021249,10021241,10021239,10021245,10021239,10021249,10021241,10021239,10021245,10021239,10021249,10021241,10021239,10021245,10021239,10021249,10021241,10021240,10021248,10021240,10021249,10021241,10021240,10021248,10021240,10021250,10021241,10021240,10021248,10021240,10021250,10021241,10021247,10021250,10021241,10021247,10021250,10021241,10021247,10021250,10021241,10021247,10021241,10021247,10021241,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021247,10021242,10021242,10021242,10021242,10021242,10021242,10021242,10021242</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L28 W10/25; N=112; EHP=4373.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x19,normal:18x20,fast:30x3,fast:58x4,fast:64x3,medium:83x5,swarm:84x31,fast:98x3,medium:108x6,medium:123x5</t>
+          <t>L28 W10/25; N=112; EHP=12258.847122; air:2x4,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x3,medium:83x5,medium:108x6,medium:123x5,normal:17x19,normal:18x20,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10021251,10021261,10021253,10049122,10021260,10021254,10021251,10021261,10021253,10049122,10021260,10021255,10021251,10021261,10021253,10049122,10021260,10021258,10021251,10021261,10021253,10049123,10021260,10021258,10021251,10021261,10021256,10049123,10021260,10045307,10021251,10021261,10021256,10049123,10021260,10021259,10021251,10021261,10021256,10049124,10021265,10021259,10021251,10021261,10021257,10049124,10021265,10021262,10021251,10021261,10021257,10049124,10021265,10021263,10021251,10021261,10021257,10049125,10021265,10021263,10021251,10021261,10021257,10049125,10021265,10045308,10021251,10021261,10021264,10049126,10021266,10021251,10021261,10021264,10049126,10021266,10021251,10021261,10021264,10049126,10021266,10021251,10021261,10021266,10021252,10021261,10021266,10021252,10021261,10021266,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021261,10021261,10021261,10021261</t>
+          <t>10021251,10049122,10021253,10049122,10021260,10021254,10021251,10049122,10021253,10049122,10021260,10021255,10021251,10049122,10021253,10049122,10021260,10021258,10021251,10049123,10021253,10049123,10021260,10021258,10021251,10049123,10021256,10049123,10021260,10045307,10021251,10049123,10021256,10049123,10021260,10021259,10021251,10049124,10021256,10049124,10021265,10021259,10021251,10049124,10021257,10049124,10021265,10021262,10021251,10049124,10021257,10049124,10021265,10021263,10021251,10049125,10021257,10049125,10021265,10021263,10021251,10049125,10021257,10049125,10021265,10045308,10021251,10049126,10021264,10049126,10021266,10021251,10049126,10021264,10049126,10021266,10021251,10049126,10021264,10049126,10021266,10021251,10021261,10021266,10021252,10021261,10021266,10021252,10021261,10021266,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021252,10021261,10021261,10021261,10021261,10021261</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L28 W11/25; N=118; EHP=4461.000000; air:2x3,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x15,normal:18x14,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x33,heavy:86x1,heavy:88x2,fast:98x3,medium:108x5,medium:123x6,heavy:127x1</t>
+          <t>L28 W11/25; N=118; EHP=12492.053756; air:2x6,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x6,medium:108x5,medium:123x6,normal:17x15,normal:18x14,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10021270,10021279,10021272,10049127,10021278,10021273,10021270,10021279,10021272,10049127,10021278,10021273,10021270,10021279,10021272,10049127,10021278,10021274,10021270,10021279,10021272,10021267,10021278,10045309,10021270,10021279,10021275,10021267,10021278,10045310,10021270,10021279,10021275,10021267,10021278,10021277,10021270,10021279,10021275,10049128,10021283,10021277,10021270,10021279,10021276,10049128,10021283,10021280,10021270,10021279,10021276,10049128,10021283,10021280,10021270,10021279,10021276,10021268,10021283,10021281,10021270,10021279,10021282,10021268,10021283,10021281,10021270,10021279,10021282,10021268,10021283,10021285,10021270,10021279,10021282,10021269,10021284,10021270,10021279,10021282,10021269,10021284,10021270,10021279,10021269,10021284,10021271,10021279,10021284,10021271,10021279,10021284,10021271,10021279,10021284,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021279,10021279,10021279</t>
+          <t>10021270,10049127,10021272,10049127,10021278,10021273,10021270,10049127,10021272,10049127,10021278,10021273,10021270,10049127,10021272,10049127,10021278,10021274,10021270,10021267,10021272,10021267,10021278,10045309,10021270,10021267,10021275,10021267,10021278,10045310,10021270,10021267,10021275,10021267,10021278,10021277,10021270,10049128,10021275,10049128,10021283,10021277,10021270,10049128,10021276,10049128,10021283,10021280,10021270,10049128,10021276,10049128,10021283,10021280,10021270,10021268,10021276,10021268,10021283,10021281,10021270,10021268,10021282,10021268,10021283,10021281,10021270,10021268,10021282,10021268,10021283,10021285,10021270,10021269,10021282,10021269,10021284,10021270,10021269,10021282,10021269,10021284,10021270,10021269,10021269,10021284,10021271,10021279,10021284,10021271,10021279,10021284,10021271,10021279,10021284,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021271,10021279,10021279,10021279,10021279</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L28 W12/25; N=124; EHP=4615.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x4,heavy:31x2,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x34,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L28 W12/25; N=124; EHP=12925.232814; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x16,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10021289,10021299,10021291,10049129,10021298,10021292,10021289,10021299,10021291,10049129,10021298,10021292,10021289,10021299,10021291,10049129,10021298,10021293,10021289,10021299,10021294,10021286,10021298,10021293,10021289,10021299,10021294,10021286,10021298,10045311,10021289,10021299,10021294,10021286,10021298,10021296,10021289,10021299,10021294,10049130,10021302,10021297,10021289,10021299,10021295,10049130,10021302,10021297,10021289,10021299,10021295,10049130,10021302,10021300,10021289,10021299,10021295,10049130,10021302,10021300,10021289,10021299,10021295,10021287,10021302,10045312,10021289,10021299,10021301,10021287,10021302,10021304,10021289,10021299,10021301,10021287,10021302,10021304,10021289,10021299,10021301,10021288,10021303,10021289,10021299,10021301,10021288,10021303,10021289,10021299,10021288,10021303,10021290,10021299,10021303,10021290,10021299,10021303,10021290,10021299,10021303,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021299,10021299,10021299,10021299,10021299</t>
+          <t>10021289,10049129,10021291,10049129,10021298,10021292,10021289,10049129,10021291,10049129,10021298,10021292,10021289,10049129,10021291,10049129,10021298,10021293,10021289,10021286,10021294,10021286,10021298,10021293,10021289,10021286,10021294,10021286,10021298,10045311,10021289,10021286,10021294,10021286,10021298,10021296,10021289,10049130,10021294,10049130,10021302,10021297,10021289,10049130,10021295,10049130,10021302,10021297,10021289,10049130,10021295,10049130,10021302,10021300,10021289,10049130,10021295,10049130,10021302,10021300,10021289,10021287,10021295,10021287,10021302,10045312,10021289,10021287,10021301,10021287,10021302,10021304,10021289,10021287,10021301,10021287,10021302,10021304,10021289,10021288,10021301,10021288,10021303,10021289,10021288,10021301,10021288,10021303,10021289,10021288,10021288,10021303,10021290,10021299,10021303,10021290,10021299,10021303,10021290,10021299,10021303,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021290,10021299,10021299,10021299,10021299,10021299,10021299</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L28 W13/25; N=130; EHP=5629.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x16,normal:18x15,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x2,heavy:88x1,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L28 W13/25; N=130; EHP=15767.939739; air:2x6,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x6,medium:108x7,medium:123x6,normal:17x16,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10021308,10021318,10021310,10049131,10021317,10021311,10021308,10021318,10021310,10049131,10021317,10021311,10021308,10021318,10021310,10049131,10021317,10021312,10021308,10021318,10021310,10049131,10021317,10021312,10021308,10021318,10021313,10021305,10021317,10021315,10021308,10021318,10021313,10021305,10021317,10021316,10021308,10021318,10021313,10021305,10021317,10021316,10021308,10021318,10021313,10049132,10021322,10045313,10021308,10021318,10021314,10049132,10021322,10021319,10021308,10021318,10021314,10049132,10021322,10021319,10021308,10021318,10021314,10021306,10021322,10021320,10021308,10021318,10021314,10021306,10021322,10021324,10021308,10021318,10021321,10021306,10021322,10021324,10021308,10021318,10021321,10021307,10021323,10021308,10021318,10021321,10021307,10021323,10021308,10021318,10021321,10021307,10021323,10021309,10021318,10021323,10021309,10021318,10021323,10021309,10021318,10021323,10021309,10021318,10021323,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021318,10021318,10021318,10021318,10021318</t>
+          <t>10021308,10049131,10021310,10049131,10021317,10021311,10021308,10049131,10021310,10049131,10021317,10021311,10021308,10049131,10021310,10049131,10021317,10021312,10021308,10049131,10021310,10049131,10021317,10021312,10021308,10021305,10021313,10021305,10021317,10021315,10021308,10021305,10021313,10021305,10021317,10021316,10021308,10021305,10021313,10021305,10021317,10021316,10021308,10049132,10021313,10049132,10021322,10045313,10021308,10049132,10021314,10049132,10021322,10021319,10021308,10049132,10021314,10049132,10021322,10021319,10021308,10021306,10021314,10021306,10021322,10021320,10021308,10021306,10021314,10021306,10021322,10021324,10021308,10021306,10021321,10021306,10021322,10021324,10021308,10021307,10021321,10021307,10021323,10021308,10021307,10021321,10021307,10021323,10021308,10021307,10021321,10021307,10021323,10021309,10021318,10021323,10021309,10021318,10021323,10021309,10021318,10021323,10021309,10021318,10021323,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021309,10021318,10021318,10021318,10021318,10021318,10021318</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L28 W14/25; N=136; EHP=6789.000000; air:2x4,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x38,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L28 W14/25; N=136; EHP=19008.110278; air:2x8,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x6,medium:123x7,normal:17x16,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10021328,10021340,10021330,10049133,10021339,10021331,10021335,10021328,10021340,10021330,10049133,10021339,10021331,10021328,10021340,10021330,10049133,10021339,10021332,10021328,10021340,10021330,10021325,10021339,10021332,10021328,10021340,10021333,10021325,10021339,10021336,10021328,10021340,10021333,10021325,10021339,10021336,10021328,10021340,10021333,10021325,10021339,10021337,10021328,10021340,10021333,10049134,10021343,10021337,10021328,10021340,10021334,10049134,10021343,10021338,10021328,10021340,10021334,10049134,10021343,10045314,10021328,10021340,10021334,10021326,10021343,10021341,10021328,10021340,10021334,10021326,10021343,10021341,10021328,10021340,10021334,10021326,10021343,10021345,10021328,10021340,10021342,10021326,10021343,10021345,10021328,10021340,10021342,10021327,10021344,10021328,10021340,10021342,10021327,10021344,10021328,10021340,10021342,10021327,10021344,10021329,10021340,10021344,10021329,10021340,10021344,10021329,10021340,10021344,10021329,10021340,10021344,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021340,10021340,10021340,10021340,10021340,10021340</t>
+          <t>10021328,10049133,10021330,10049133,10021339,10021331,10021335,10021328,10049133,10021330,10049133,10021339,10021331,10021328,10049133,10021330,10049133,10021339,10021332,10021328,10021325,10021330,10021325,10021339,10021332,10021328,10021325,10021333,10021325,10021339,10021336,10021328,10021325,10021333,10021325,10021339,10021336,10021328,10021325,10021333,10021325,10021339,10021337,10021328,10049134,10021333,10049134,10021343,10021337,10021328,10049134,10021334,10049134,10021343,10021338,10021328,10049134,10021334,10049134,10021343,10045314,10021328,10021326,10021334,10021326,10021343,10021341,10021328,10021326,10021334,10021326,10021343,10021341,10021328,10021326,10021334,10021326,10021343,10021345,10021328,10021326,10021342,10021326,10021343,10021345,10021328,10021327,10021342,10021327,10021344,10021328,10021327,10021342,10021327,10021344,10021328,10021327,10021342,10021327,10021344,10021329,10021340,10021344,10021329,10021340,10021344,10021329,10021340,10021344,10021329,10021340,10021344,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021329,10021340,10021340,10021340,10021340,10021340,10021340,10021340</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L28 W15/25; N=142; EHP=11847.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x39,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L28 W15/25; N=142; EHP=33165.210366; air:2x6,air:11x8,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x16,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10021346,10021356,10021348,10049135,10021355,10045315,10021346,10021356,10021348,10049135,10021355,10021349,10021346,10021356,10021348,10049135,10021355,10021349,10021346,10021356,10021348,10049136,10021355,10021352,10021346,10021356,10021348,10049136,10021355,10021352,10021346,10021356,10021350,10049136,10021355,10021353,10021346,10021356,10021350,10049136,10021355,10021353,10021346,10021356,10021350,10049137,10021360,10021354,10021346,10021356,10021350,10049137,10021360,10021354,10021346,10021356,10021351,10049137,10021360,10021357,10021346,10021356,10021351,10049137,10021360,10021358,10021346,10021356,10021351,10049138,10021360,10021358,10021346,10021356,10021351,10049138,10021360,10021362,10021346,10021356,10021359,10049138,10021360,10021362,10021346,10021356,10021359,10049139,10021360,10021346,10021356,10021359,10049139,10021361,10021346,10021356,10021359,10049139,10021361,10021346,10021356,10049139,10021361,10021347,10021356,10021361,10021347,10021356,10021361,10021347,10021356,10021361,10021347,10021356,10021361,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021356,10021356,10021356,10021356,10021356</t>
+          <t>10021346,10049135,10021348,10049135,10021355,10045315,10021346,10049135,10021348,10049135,10021355,10021349,10021346,10049135,10021348,10049135,10021355,10021349,10021346,10049136,10021348,10049136,10021355,10021352,10021346,10049136,10021348,10049136,10021355,10021352,10021346,10049136,10021350,10049136,10021355,10021353,10021346,10049136,10021350,10049136,10021355,10021353,10021346,10049137,10021350,10049137,10021360,10021354,10021346,10049137,10021350,10049137,10021360,10021354,10021346,10049137,10021351,10049137,10021360,10021357,10021346,10049137,10021351,10049137,10021360,10021358,10021346,10049138,10021351,10049138,10021360,10021358,10021346,10049138,10021351,10049138,10021360,10021362,10021346,10049138,10021359,10049138,10021360,10021362,10021346,10049139,10021359,10049139,10021360,10021346,10049139,10021359,10049139,10021361,10021346,10049139,10021359,10049139,10021361,10021346,10049139,10049139,10021361,10021347,10021356,10021361,10021347,10021356,10021361,10021347,10021356,10021361,10021347,10021356,10021361,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021347,10021356,10021356,10021356,10021356,10021356,10021356</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L28 W16/25; N=148; EHP=12084.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x18,fast:30x5,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x41,heavy:86x1,heavy:88x2,fast:98x4,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L28 W16/25; N=148; EHP=33846.459707; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x5,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x7,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10021366,10021376,10021368,10049140,10021375,10021369,10021366,10021376,10021368,10049140,10021375,10021369,10021366,10021376,10021368,10049140,10021375,10045316,10021366,10021376,10021368,10049140,10021375,10021372,10021366,10021376,10021370,10021363,10021375,10021372,10021366,10021376,10021370,10021363,10021375,10021373,10021366,10021376,10021370,10021363,10021375,10021373,10021366,10021376,10021370,10049141,10021375,10021374,10021366,10021376,10021370,10049141,10021380,10021374,10021366,10021376,10021371,10049141,10021380,10021377,10021366,10021376,10021371,10049141,10021380,10021377,10021366,10021376,10021371,10021364,10021380,10021378,10021366,10021376,10021371,10021364,10021380,10021378,10021366,10021376,10021379,10021364,10021380,10021382,10021366,10021376,10021379,10021365,10021380,10021382,10021366,10021376,10021379,10021365,10021381,10021366,10021376,10021379,10021365,10021381,10021366,10021376,10021379,10021365,10021381,10021366,10021376,10021381,10021367,10021376,10021381,10021367,10021376,10021381,10021367,10021376,10021381,10021367,10021376,10021381,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021376,10021376,10021376,10021376,10021376,10021376</t>
+          <t>10021366,10049140,10021368,10049140,10021375,10021369,10021366,10049140,10021368,10049140,10021375,10021369,10021366,10049140,10021368,10049140,10021375,10045316,10021366,10049140,10021368,10049140,10021375,10021372,10021366,10021363,10021370,10021363,10021375,10021372,10021366,10021363,10021370,10021363,10021375,10021373,10021366,10021363,10021370,10021363,10021375,10021373,10021366,10049141,10021370,10049141,10021375,10021374,10021366,10049141,10021370,10049141,10021380,10021374,10021366,10049141,10021371,10049141,10021380,10021377,10021366,10049141,10021371,10049141,10021380,10021377,10021366,10021364,10021371,10021364,10021380,10021378,10021366,10021364,10021371,10021364,10021380,10021378,10021366,10021364,10021379,10021364,10021380,10021382,10021366,10021365,10021379,10021365,10021380,10021382,10021366,10021365,10021379,10021365,10021381,10021366,10021365,10021379,10021365,10021381,10021366,10021365,10021379,10021365,10021381,10021366,10021376,10021381,10021367,10021376,10021381,10021367,10021376,10021381,10021367,10021376,10021381,10021367,10021376,10021381,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021367,10021376,10021376,10021376,10021376,10021376,10021376,10021376</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L28 W17/25; N=154; EHP=12326.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x18,fast:30x4,heavy:31x2,heavy:40x1,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L28 W17/25; N=154; EHP=34506.691592; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x8,normal:17x19,normal:18x18,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10021386,10021397,10021388,10049142,10021396,10021389,10021386,10021397,10021388,10049142,10021396,10021389,10021386,10021397,10021388,10049142,10021396,10021390,10021386,10021397,10021388,10049142,10021396,10021390,10021386,10021397,10021388,10021383,10021396,10021393,10021386,10021397,10021391,10021383,10021396,10021393,10021386,10021397,10021391,10021383,10021396,10021394,10021386,10021397,10021391,10021383,10021396,10021394,10021386,10021397,10021391,10049143,10021401,10021395,10021386,10021397,10021391,10049143,10021401,10021395,10021386,10021397,10021392,10049143,10021401,10021398,10021386,10021397,10021392,10049143,10021401,10021398,10021386,10021397,10021392,10021384,10021401,10021399,10021386,10021397,10021392,10021384,10021401,10021399,10021386,10021397,10021392,10021384,10021401,10045317,10021386,10021397,10021400,10021384,10021401,10045317,10021386,10021397,10021400,10021385,10021402,10021386,10021397,10021400,10021385,10021402,10021386,10021397,10021400,10021385,10021402,10021387,10021397,10021402,10021387,10021397,10021402,10021387,10021397,10021402,10021387,10021397,10021402,10021387,10021397,10021402,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021397,10021397,10021397,10021397,10021397,10021397</t>
+          <t>10021386,10049142,10021388,10049142,10021396,10021389,10021386,10049142,10021388,10049142,10021396,10021389,10021386,10049142,10021388,10049142,10021396,10021390,10021386,10049142,10021388,10049142,10021396,10021390,10021386,10021383,10021388,10021383,10021396,10021393,10021386,10021383,10021391,10021383,10021396,10021393,10021386,10021383,10021391,10021383,10021396,10021394,10021386,10021383,10021391,10021383,10021396,10021394,10021386,10049143,10021391,10049143,10021401,10021395,10021386,10049143,10021391,10049143,10021401,10021395,10021386,10049143,10021392,10049143,10021401,10021398,10021386,10049143,10021392,10049143,10021401,10021398,10021386,10021384,10021392,10021384,10021401,10021399,10021386,10021384,10021392,10021384,10021401,10021399,10021386,10021384,10021392,10021384,10021401,10045317,10021386,10021384,10021400,10021384,10021401,10045317,10021386,10021385,10021400,10021385,10021402,10021386,10021385,10021400,10021385,10021402,10021386,10021385,10021400,10021385,10021402,10021387,10021397,10021402,10021387,10021397,10021402,10021387,10021397,10021402,10021387,10021397,10021402,10021387,10021397,10021402,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021387,10021397,10021397,10021397,10021397,10021397,10021397,10021397</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L28 W18/25; N=160; EHP=13169.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x3,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L28 W18/25; N=160; EHP=36871.719418; air:2x8,air:11x8,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10021406,10021417,10021408,10049144,10021416,10021409,10021406,10021417,10021408,10049144,10021416,10021409,10021406,10021417,10021408,10049144,10021416,10021410,10021406,10021417,10021408,10049144,10021416,10021410,10021406,10021417,10021408,10021403,10021416,10021413,10021406,10021417,10021411,10021403,10021416,10021413,10021406,10021417,10021411,10021403,10021416,10021414,10021406,10021417,10021411,10021403,10021416,10021414,10021406,10021417,10021411,10049145,10021421,10021415,10021406,10021417,10021412,10049145,10021421,10021415,10021406,10021417,10021412,10049145,10021421,10021418,10021406,10021417,10021412,10049145,10021421,10021418,10021406,10021417,10021412,10021404,10021421,10021419,10021406,10021417,10021412,10021404,10021421,10021419,10021406,10021417,10021420,10021404,10021421,10021423,10021406,10021417,10021420,10021404,10021421,10021423,10021406,10021417,10021420,10021405,10021422,10021406,10021417,10021420,10021405,10021422,10021406,10021417,10021420,10021405,10021422,10021406,10021417,10021405,10021422,10021406,10021417,10021422,10021407,10021417,10021422,10021407,10021417,10021422,10021407,10021417,10021422,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021417,10021417,10021417,10021417,10021417</t>
+          <t>10021406,10049144,10021408,10049144,10021416,10021409,10021406,10049144,10021408,10049144,10021416,10021409,10021406,10049144,10021408,10049144,10021416,10021410,10021406,10049144,10021408,10049144,10021416,10021410,10021406,10021403,10021408,10021403,10021416,10021413,10021406,10021403,10021411,10021403,10021416,10021413,10021406,10021403,10021411,10021403,10021416,10021414,10021406,10021403,10021411,10021403,10021416,10021414,10021406,10049145,10021411,10049145,10021421,10021415,10021406,10049145,10021412,10049145,10021421,10021415,10021406,10049145,10021412,10049145,10021421,10021418,10021406,10049145,10021412,10049145,10021421,10021418,10021406,10021404,10021412,10021404,10021421,10021419,10021406,10021404,10021412,10021404,10021421,10021419,10021406,10021404,10021420,10021404,10021421,10021423,10021406,10021404,10021420,10021404,10021421,10021423,10021406,10021405,10021420,10021405,10021422,10021406,10021405,10021420,10021405,10021422,10021406,10021405,10021420,10021405,10021422,10021406,10021405,10021405,10021422,10021406,10021417,10021422,10021407,10021417,10021422,10021407,10021417,10021422,10021407,10021417,10021422,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021407,10021417,10021417,10021417,10021417,10021417,10021417</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L28 W19/25; N=166; EHP=15253.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L28 W19/25; N=166; EHP=42717.988629; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x4,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x21,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10021427,10021439,10021429,10049146,10021438,10021430,10021434,10021427,10021439,10021429,10049146,10021438,10021430,10021427,10021439,10021429,10049146,10021438,10021431,10021427,10021439,10021429,10049146,10021438,10021431,10021427,10021439,10021429,10021424,10021438,10021435,10021427,10021439,10021432,10021424,10021438,10021435,10021427,10021439,10021432,10021424,10021438,10021436,10021427,10021439,10021432,10021424,10021438,10021436,10021427,10021439,10021432,10049147,10021438,10021437,10021427,10021439,10021432,10049147,10021443,10021437,10021427,10021439,10021433,10049147,10021443,10021440,10021427,10021439,10021433,10049147,10021443,10021440,10021427,10021439,10021433,10021425,10021443,10021441,10021427,10021439,10021433,10021425,10021443,10021441,10021427,10021439,10021433,10021425,10021443,10021441,10021427,10021439,10021442,10021425,10021443,10021445,10021427,10021439,10021442,10021425,10021443,10021445,10021427,10021439,10021442,10021426,10021444,10021427,10021439,10021442,10021426,10021444,10021427,10021439,10021442,10021426,10021444,10021428,10021439,10021426,10021444,10021428,10021439,10021444,10021428,10021439,10021444,10021428,10021439,10021444,10021428,10021439,10021444,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021439,10021439,10021439,10021439,10021439,10021439,10021439,10021439</t>
+          <t>10021427,10049146,10021429,10049146,10021438,10021430,10021434,10021427,10049146,10021429,10049146,10021438,10021430,10021427,10049146,10021429,10049146,10021438,10021431,10021427,10049146,10021429,10049146,10021438,10021431,10021427,10021424,10021429,10021424,10021438,10021435,10021427,10021424,10021432,10021424,10021438,10021435,10021427,10021424,10021432,10021424,10021438,10021436,10021427,10021424,10021432,10021424,10021438,10021436,10021427,10049147,10021432,10049147,10021438,10021437,10021427,10049147,10021432,10049147,10021443,10021437,10021427,10049147,10021433,10049147,10021443,10021440,10021427,10049147,10021433,10049147,10021443,10021440,10021427,10021425,10021433,10021425,10021443,10021441,10021427,10021425,10021433,10021425,10021443,10021441,10021427,10021425,10021433,10021425,10021443,10021441,10021427,10021425,10021442,10021425,10021443,10021445,10021427,10021425,10021442,10021425,10021443,10021445,10021427,10021426,10021442,10021426,10021444,10021427,10021426,10021442,10021426,10021444,10021427,10021426,10021442,10021426,10021444,10021428,10021426,10021426,10021444,10021428,10021439,10021444,10021428,10021439,10021444,10021428,10021439,10021444,10021428,10021439,10021444,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021428,10021439,10021439,10021439,10021439,10021439,10021439,10021439,10021439,10021439</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L28 W20/25; N=172; EHP=25599.000000; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x48,heavy:86x2,heavy:88x3,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L28 W20/25; N=172; EHP=71685.623531; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10021449,10021460,10021451,10049148,10021459,10021452,10021449,10021460,10021451,10049148,10021459,10021452,10021449,10021460,10021451,10049148,10021459,10021453,10021449,10021460,10021451,10049148,10021459,10021453,10021449,10021460,10021451,10021446,10021459,10021456,10021449,10021460,10021454,10021446,10021459,10021456,10021449,10021460,10021454,10021446,10021459,10021457,10021449,10021460,10021454,10021446,10021459,10021457,10021449,10021460,10021454,10021446,10021464,10021458,10021449,10021460,10021454,10049149,10021464,10021458,10021449,10021460,10021455,10049149,10021464,10021458,10021449,10021460,10021455,10049149,10021464,10021461,10021449,10021460,10021455,10049149,10021464,10021461,10021449,10021460,10021455,10021447,10021464,10021462,10021449,10021460,10021455,10021447,10021464,10021462,10021449,10021460,10021463,10021447,10021464,10021466,10021449,10021460,10021463,10021447,10021464,10021466,10021449,10021460,10021463,10021448,10021465,10021449,10021460,10021463,10021448,10021465,10021449,10021460,10021463,10021448,10021465,10021449,10021460,10021463,10021448,10021465,10021449,10021460,10021465,10021450,10021460,10021465,10021450,10021460,10021465,10021450,10021460,10021465,10021450,10021460,10021465,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021460,10021460,10021460,10021460,10021460</t>
+          <t>10021449,10049148,10021451,10049148,10021459,10021452,10021449,10049148,10021451,10049148,10021459,10021452,10021449,10049148,10021451,10049148,10021459,10021453,10021449,10049148,10021451,10049148,10021459,10021453,10021449,10021446,10021451,10021446,10021459,10021456,10021449,10021446,10021454,10021446,10021459,10021456,10021449,10021446,10021454,10021446,10021459,10021457,10021449,10021446,10021454,10021446,10021459,10021457,10021449,10021446,10021454,10021446,10021464,10021458,10021449,10049149,10021454,10049149,10021464,10021458,10021449,10049149,10021455,10049149,10021464,10021458,10021449,10049149,10021455,10049149,10021464,10021461,10021449,10049149,10021455,10049149,10021464,10021461,10021449,10021447,10021455,10021447,10021464,10021462,10021449,10021447,10021455,10021447,10021464,10021462,10021449,10021447,10021463,10021447,10021464,10021466,10021449,10021447,10021463,10021447,10021464,10021466,10021449,10021448,10021463,10021448,10021465,10021449,10021448,10021463,10021448,10021465,10021449,10021448,10021463,10021448,10021465,10021449,10021448,10021463,10021448,10021465,10021449,10021460,10021465,10021450,10021460,10021465,10021450,10021460,10021465,10021450,10021460,10021465,10021450,10021460,10021465,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021450,10021460,10021460,10021460,10021460,10021460,10021460</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L28 W21/25; N=178; EHP=26111.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x8,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L28 W21/25; N=178; EHP=73108.577669; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10021470,10021481,10021472,10049150,10021480,10021473,10021470,10021481,10021472,10049150,10021480,10021473,10021470,10021481,10021472,10049150,10021480,10021473,10021470,10021481,10021472,10049150,10021480,10021474,10021470,10021481,10021472,10021467,10021480,10021474,10021470,10021481,10021475,10021467,10021480,10021477,10021470,10021481,10021475,10021467,10021480,10021477,10021470,10021481,10021475,10021467,10021480,10021478,10021470,10021481,10021475,10049151,10021480,10021478,10021470,10021481,10021475,10049151,10021485,10021479,10021470,10021481,10021475,10049151,10021485,10021479,10021470,10021481,10021476,10049151,10021485,10021482,10021470,10021481,10021476,10049151,10021485,10021482,10021470,10021481,10021476,10021468,10021485,10021482,10021470,10021481,10021476,10021468,10021485,10021483,10021470,10021481,10021476,10021468,10021485,10021483,10021470,10021481,10021476,10021468,10021485,10021487,10021470,10021481,10021484,10021469,10021485,10021487,10021470,10021481,10021484,10021469,10021486,10021470,10021481,10021484,10021469,10021486,10021470,10021481,10021484,10021469,10021486,10021470,10021481,10021484,10021469,10021486,10021471,10021481,10021486,10021471,10021481,10021486,10021471,10021481,10021486,10021471,10021481,10021486,10021471,10021481,10021486,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021481,10021481,10021481,10021481,10021481,10021481,10021481</t>
+          <t>10021470,10049150,10021472,10049150,10021480,10021473,10021470,10049150,10021472,10049150,10021480,10021473,10021470,10049150,10021472,10049150,10021480,10021473,10021470,10049150,10021472,10049150,10021480,10021474,10021470,10021467,10021472,10021467,10021480,10021474,10021470,10021467,10021475,10021467,10021480,10021477,10021470,10021467,10021475,10021467,10021480,10021477,10021470,10021467,10021475,10021467,10021480,10021478,10021470,10049151,10021475,10049151,10021480,10021478,10021470,10049151,10021475,10049151,10021485,10021479,10021470,10049151,10021475,10049151,10021485,10021479,10021470,10049151,10021476,10049151,10021485,10021482,10021470,10049151,10021476,10049151,10021485,10021482,10021470,10021468,10021476,10021468,10021485,10021482,10021470,10021468,10021476,10021468,10021485,10021483,10021470,10021468,10021476,10021468,10021485,10021483,10021470,10021468,10021476,10021468,10021485,10021487,10021470,10021469,10021484,10021469,10021485,10021487,10021470,10021469,10021484,10021469,10021486,10021470,10021469,10021484,10021469,10021486,10021470,10021469,10021484,10021469,10021486,10021470,10021469,10021484,10021469,10021486,10021471,10021481,10021486,10021471,10021481,10021486,10021471,10021481,10021486,10021471,10021481,10021486,10021471,10021481,10021486,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021471,10021481,10021481,10021481,10021481,10021481,10021481,10021481,10021481</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L28 W22/25; N=184; EHP=26634.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x5,normal:17x22,normal:18x22,fast:30x5,heavy:31x3,heavy:40x2,fast:58x6,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x51,heavy:86x3,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L28 W22/25; N=184; EHP=74583.002102; air:2x8,air:11x8,air:12x10,air:13x8,air:14x10,fast:30x5,fast:58x6,fast:64x6,fast:98x5,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10021491,10021502,10021493,10049152,10021501,10021494,10021491,10021502,10021493,10049152,10021501,10021494,10021491,10021502,10021493,10049152,10021501,10021494,10021491,10021502,10021493,10049152,10021501,10021495,10021491,10021502,10021493,10049152,10021501,10021495,10021491,10021502,10021493,10021488,10021501,10021495,10021491,10021502,10021496,10021488,10021501,10021498,10021491,10021502,10021496,10021488,10021501,10021498,10021491,10021502,10021496,10021488,10021501,10021499,10021491,10021502,10021496,10049153,10021501,10021499,10021491,10021502,10021496,10049153,10021506,10021500,10021491,10021502,10021497,10049153,10021506,10021500,10021491,10021502,10021497,10049153,10021506,10021503,10021491,10021502,10021497,10049153,10021506,10021503,10021491,10021502,10021497,10021489,10021506,10021504,10021491,10021502,10021497,10021489,10021506,10021504,10021491,10021502,10021497,10021489,10021506,10021508,10021491,10021502,10021505,10021489,10021506,10021508,10021491,10021502,10021505,10021489,10021506,10021508,10021491,10021502,10021505,10021490,10021507,10021491,10021502,10021505,10021490,10021507,10021491,10021502,10021505,10021490,10021507,10021491,10021502,10021490,10021507,10021492,10021502,10021507,10021492,10021502,10021507,10021492,10021502,10021507,10021492,10021502,10021507,10021492,10021502,10021507,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021502,10021502,10021502,10021502,10021502,10021502,10021502,10021502</t>
+          <t>10021491,10049152,10021493,10049152,10021501,10021494,10021491,10049152,10021493,10049152,10021501,10021494,10021491,10049152,10021493,10049152,10021501,10021494,10021491,10049152,10021493,10049152,10021501,10021495,10021491,10049152,10021493,10049152,10021501,10021495,10021491,10021488,10021493,10021488,10021501,10021495,10021491,10021488,10021496,10021488,10021501,10021498,10021491,10021488,10021496,10021488,10021501,10021498,10021491,10021488,10021496,10021488,10021501,10021499,10021491,10049153,10021496,10049153,10021501,10021499,10021491,10049153,10021496,10049153,10021506,10021500,10021491,10049153,10021497,10049153,10021506,10021500,10021491,10049153,10021497,10049153,10021506,10021503,10021491,10049153,10021497,10049153,10021506,10021503,10021491,10021489,10021497,10021489,10021506,10021504,10021491,10021489,10021497,10021489,10021506,10021504,10021491,10021489,10021497,10021489,10021506,10021508,10021491,10021489,10021505,10021489,10021506,10021508,10021491,10021489,10021505,10021489,10021506,10021508,10021491,10021490,10021505,10021490,10021507,10021491,10021490,10021505,10021490,10021507,10021491,10021490,10021505,10021490,10021507,10021491,10021490,10021490,10021507,10021492,10021502,10021507,10021492,10021502,10021507,10021492,10021502,10021507,10021492,10021502,10021507,10021492,10021502,10021507,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021492,10021502,10021502,10021502,10021502,10021502,10021502,10021502,10021502,10021502</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L28 W23/25; N=190; EHP=27167.000000; air:2x5,air:11x4,air:12x5,air:13x5,air:14x4,normal:17x23,normal:18x22,fast:30x6,heavy:31x3,heavy:40x3,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x10,swarm:84x53,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x3</t>
+          <t>L28 W23/25; N=190; EHP=76084.490476; air:2x10,air:11x8,air:12x10,air:13x10,air:14x8,fast:30x6,fast:58x5,fast:64x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x10,medium:108x9,medium:123x9,normal:17x23,normal:18x22,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10021512,10021523,10021514,10049154,10021522,10021515,10021512,10021523,10021514,10049154,10021522,10021515,10021512,10021523,10021514,10049154,10021522,10021516,10021512,10021523,10021514,10049154,10021522,10021516,10021512,10021523,10021514,10049154,10021522,10021516,10021512,10021523,10021514,10021509,10021522,10021519,10021512,10021523,10021517,10021509,10021522,10021519,10021512,10021523,10021517,10021509,10021522,10021520,10021512,10021523,10021517,10021509,10021522,10021520,10021512,10021523,10021517,10021509,10021527,10021520,10021512,10021523,10021517,10049155,10021527,10021521,10021512,10021523,10021517,10049155,10021527,10021521,10021512,10021523,10021518,10049155,10021527,10021524,10021512,10021523,10021518,10049155,10021527,10021524,10021512,10021523,10021518,10021510,10021527,10021525,10021512,10021523,10021518,10021510,10021527,10021525,10021512,10021523,10021518,10021510,10021527,10021529,10021512,10021523,10021526,10021510,10021527,10021529,10021512,10021523,10021526,10021510,10021527,10021529,10021512,10021523,10021526,10021511,10021528,10021512,10021523,10021526,10021511,10021528,10021512,10021523,10021526,10021511,10021528,10021512,10021523,10021526,10021511,10021528,10021513,10021523,10021511,10021528,10021513,10021523,10021528,10021513,10021523,10021528,10021513,10021523,10021528,10021513,10021523,10021528,10021513,10021523,10021528,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021523,10021523,10021523,10021523,10021523,10021523,10021523</t>
+          <t>10021512,10049154,10021514,10049154,10021522,10021515,10021512,10049154,10021514,10049154,10021522,10021515,10021512,10049154,10021514,10049154,10021522,10021516,10021512,10049154,10021514,10049154,10021522,10021516,10021512,10049154,10021514,10049154,10021522,10021516,10021512,10021509,10021514,10021509,10021522,10021519,10021512,10021509,10021517,10021509,10021522,10021519,10021512,10021509,10021517,10021509,10021522,10021520,10021512,10021509,10021517,10021509,10021522,10021520,10021512,10021509,10021517,10021509,10021527,10021520,10021512,10049155,10021517,10049155,10021527,10021521,10021512,10049155,10021517,10049155,10021527,10021521,10021512,10049155,10021518,10049155,10021527,10021524,10021512,10049155,10021518,10049155,10021527,10021524,10021512,10021510,10021518,10021510,10021527,10021525,10021512,10021510,10021518,10021510,10021527,10021525,10021512,10021510,10021518,10021510,10021527,10021529,10021512,10021510,10021526,10021510,10021527,10021529,10021512,10021510,10021526,10021510,10021527,10021529,10021512,10021511,10021526,10021511,10021528,10021512,10021511,10021526,10021511,10021528,10021512,10021511,10021526,10021511,10021528,10021512,10021511,10021526,10021511,10021528,10021513,10021511,10021511,10021528,10021513,10021523,10021528,10021513,10021523,10021528,10021513,10021523,10021528,10021513,10021523,10021528,10021513,10021523,10021528,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021513,10021523,10021523,10021523,10021523,10021523,10021523,10021523,10021523</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L28 W24/25; N=196; EHP=29092.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x23,normal:18x24,fast:30x6,heavy:31x2,heavy:40x3,fast:58x6,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x54,heavy:86x2,heavy:88x2,fast:98x6,medium:108x10,medium:123x10,heavy:127x3</t>
+          <t>L28 W24/25; N=196; EHP=81489.273011; air:2x10,air:11x10,air:12x8,air:13x10,air:14x10,fast:30x6,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x10,medium:123x10,normal:17x23,normal:18x24,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10021533,10021544,10021535,10049156,10021543,10021536,10021551,10021533,10021544,10021535,10049156,10021543,10021536,10021533,10021544,10021535,10049156,10021543,10021537,10021533,10021544,10021535,10049156,10021543,10021537,10021533,10021544,10021535,10021530,10021543,10021540,10021533,10021544,10021535,10021530,10021543,10021540,10021533,10021544,10021538,10021530,10021543,10021540,10021533,10021544,10021538,10021530,10021543,10021541,10021533,10021544,10021538,10021530,10021543,10021541,10021533,10021544,10021538,10049157,10021543,10021541,10021533,10021544,10021538,10049157,10021548,10021542,10021533,10021544,10021538,10049157,10021548,10021542,10021533,10021544,10021539,10049157,10021548,10021545,10021533,10021544,10021539,10049157,10021548,10021545,10021533,10021544,10021539,10021531,10021548,10021546,10021533,10021544,10021539,10021531,10021548,10021546,10021533,10021544,10021539,10021531,10021548,10021546,10021533,10021544,10021539,10021531,10021548,10021550,10021533,10021544,10021547,10021531,10021548,10021550,10021533,10021544,10021547,10021532,10021548,10021550,10021533,10021544,10021547,10021532,10021549,10021533,10021544,10021547,10021532,10021549,10021533,10021544,10021547,10021532,10021549,10021533,10021544,10021547,10021532,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021544,10021544,10021544,10021544,10021544,10021544,10021544,10021544,10021544</t>
+          <t>10021533,10049156,10021535,10049156,10021543,10021536,10021551,10021533,10049156,10021535,10049156,10021543,10021536,10021533,10049156,10021535,10049156,10021543,10021537,10021533,10049156,10021535,10049156,10021543,10021537,10021533,10021530,10021535,10021530,10021543,10021540,10021533,10021530,10021535,10021530,10021543,10021540,10021533,10021530,10021538,10021530,10021543,10021540,10021533,10021530,10021538,10021530,10021543,10021541,10021533,10021530,10021538,10021530,10021543,10021541,10021533,10049157,10021538,10049157,10021543,10021541,10021533,10049157,10021538,10049157,10021548,10021542,10021533,10049157,10021538,10049157,10021548,10021542,10021533,10049157,10021539,10049157,10021548,10021545,10021533,10049157,10021539,10049157,10021548,10021545,10021533,10021531,10021539,10021531,10021548,10021546,10021533,10021531,10021539,10021531,10021548,10021546,10021533,10021531,10021539,10021531,10021548,10021546,10021533,10021531,10021539,10021531,10021548,10021550,10021533,10021531,10021547,10021531,10021548,10021550,10021533,10021532,10021547,10021532,10021548,10021550,10021533,10021532,10021547,10021532,10021549,10021533,10021532,10021547,10021532,10021549,10021533,10021532,10021547,10021532,10021549,10021533,10021532,10021547,10021532,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021549,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021534,10021544,10021544,10021544,10021544,10021544,10021544,10021544,10021544,10021544,10021544</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L28 W25/25; N=202; EHP=58060.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x24,normal:18x23,fast:30x6,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x10,swarm:84x56,heavy:86x2,heavy:88x3,fast:98x6,medium:108x10,medium:123x10,heavy:127x3,boss:132x1</t>
+          <t>L28 W25/25; N=202; EHP=162533.625384; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x3,medium:83x10,medium:108x10,medium:123x10,normal:17x24,normal:18x23,swarm:84x32 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L28/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L28/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>226</v>
+        <v>380</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>219</v>
+        <v>340</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>212</v>
+        <v>300</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>205</v>
+        <v>390</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>198</v>
+        <v>330</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>191</v>
+        <v>310</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>184</v>
+        <v>390</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>177</v>
+        <v>320</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>163</v>
+        <v>310</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>156</v>
+        <v>330</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>149</v>
+        <v>300</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>142</v>
+        <v>390</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>135</v>
+        <v>310</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
